--- a/Test data file 01.xlsx
+++ b/Test data file 01.xlsx
@@ -468,7 +468,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="2">
-        <v>9025325123</v>
+        <v>9840255578</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
